--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/supermercado-150j-20m-5_20tr-lognormald-48c_ljf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/supermercado-150j-20m-5_20tr-lognormald-48c_ljf.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Compra #FH239</t>
+          <t>Compra #UX090</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,138 +479,138 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Compra #NN046</t>
+          <t>Compra #EU242</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compra #SX689</t>
+          <t>Compra #UA701</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compra #EH916</t>
+          <t>Compra #HF244</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compra #HU805</t>
+          <t>Compra #FS108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compra #AU021</t>
+          <t>Compra #XE682</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compra #SF808</t>
+          <t>Compra #NH579</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compra #HN989</t>
+          <t>Compra #FS673</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -626,40 +626,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Compra #FU595</t>
+          <t>Compra #NU117</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compra #XN310</t>
+          <t>Compra #ET827</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>19</v>
@@ -668,61 +668,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Compra #FA503</t>
+          <t>Compra #FX788</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compra #FH159</t>
+          <t>Compra #FA454</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compra #XX032</t>
+          <t>Compra #UU484</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
         <v>38</v>
@@ -731,12 +731,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Compra #TA630</t>
+          <t>Compra #AX964</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -752,12 +752,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compra #SA266</t>
+          <t>Compra #UN066</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -773,124 +773,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Compra #TT159</t>
+          <t>Compra #TE060</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Compra #XN403</t>
+          <t>Compra #AF629</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Compra #AU258</t>
+          <t>Compra #TU020</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Compra #AX942</t>
+          <t>Compra #EN109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compra #FT683</t>
+          <t>Compra #HT866</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Compra #XE764</t>
+          <t>Compra #AS891</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
         <v>44</v>
@@ -899,12 +899,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Compra #SE883</t>
+          <t>Compra #AN636</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -920,12 +920,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Compra #HF916</t>
+          <t>Compra #AT801</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -941,1629 +941,1629 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Compra #SF562</t>
+          <t>Compra #AE532</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Compra #NT528</t>
+          <t>Compra #NU981</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Compra #NT666</t>
+          <t>Compra #FH479</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Compra #TE731</t>
+          <t>Compra #EH620</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Compra #XX568</t>
+          <t>Compra #FN297</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Compra #HH281</t>
+          <t>Compra #SF493</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Compra #HT606</t>
+          <t>Compra #TF107</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Compra #XU821</t>
+          <t>Compra #HN220</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Compra #XA788</t>
+          <t>Compra #SU088</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Compra #SX609</t>
+          <t>Compra #TA108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Compra #NU838</t>
+          <t>Compra #AF747</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Compra #TU574</t>
+          <t>Compra #TF554</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Compra #HS102</t>
+          <t>Compra #HH210</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Compra #EX699</t>
+          <t>Compra #NF995</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Compra #TT594</t>
+          <t>Compra #TU041</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Compra #EH349</t>
+          <t>Compra #NH676</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Compra #AS623</t>
+          <t>Compra #XH876</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Compra #XF163</t>
+          <t>Compra #SN277</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Compra #SA389</t>
+          <t>Compra #AT596</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Compra #EA987</t>
+          <t>Compra #AS087</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Compra #FU134</t>
+          <t>Compra #FX224</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Compra #XH309</t>
+          <t>Compra #XX372</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E46" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Compra #SU330</t>
+          <t>Compra #US936</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Compra #EF321</t>
+          <t>Compra #XE348</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Compra #EF196</t>
+          <t>Compra #TN870</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Compra #XH821</t>
+          <t>Compra #FE461</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Compra #EA466</t>
+          <t>Compra #NH970</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Compra #NH276</t>
+          <t>Compra #UA927</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Compra #UN351</t>
+          <t>Compra #AH503</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Compra #UX515</t>
+          <t>Compra #AU481</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Compra #NE115</t>
+          <t>Compra #HU961</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Compra #SX246</t>
+          <t>Compra #XT218</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Compra #NN563</t>
+          <t>Compra #NX713</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Compra #TA840</t>
+          <t>Compra #NH786</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E58" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Compra #EE629</t>
+          <t>Compra #AA331</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Compra #SU969</t>
+          <t>Compra #XS934</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="E60" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Compra #UT861</t>
+          <t>Compra #AH370</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Compra #SA764</t>
+          <t>Compra #XS559</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E62" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Compra #XT217</t>
+          <t>Compra #HN087</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Compra #FS369</t>
+          <t>Compra #FA543</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Compra #XU940</t>
+          <t>Compra #XN703</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E65" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Compra #TN340</t>
+          <t>Compra #XA825</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Compra #FT561</t>
+          <t>Compra #NF899</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Compra #SN780</t>
+          <t>Compra #NA138</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Compra #UT964</t>
+          <t>Compra #EX416</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Compra #AH254</t>
+          <t>Compra #TT070</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Compra #TT631</t>
+          <t>Compra #UF929</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Compra #AU076</t>
+          <t>Compra #FN370</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E72" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Compra #HA739</t>
+          <t>Compra #XN598</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>7</v>
       </c>
       <c r="D73" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Compra #AE598</t>
+          <t>Compra #HF409</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Compra #HT619</t>
+          <t>Compra #AH404</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Compra #AN638</t>
+          <t>Compra #SS440</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E76" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Compra #UU779</t>
+          <t>Compra #AT744</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Compra #ES740</t>
+          <t>Compra #AT819</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Compra #FU792</t>
+          <t>Compra #SS974</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E79" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Compra #HS824</t>
+          <t>Compra #EE291</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E80" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Compra #NH463</t>
+          <t>Compra #TE891</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Compra #XT510</t>
+          <t>Compra #FT660</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Compra #AX720</t>
+          <t>Compra #XU805</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Compra #AN655</t>
+          <t>Compra #TF963</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Compra #ET737</t>
+          <t>Compra #FS976</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E85" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Compra #UT969</t>
+          <t>Compra #TE659</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E86" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Compra #ES964</t>
+          <t>Compra #NE962</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E87" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Compra #XT482</t>
+          <t>Compra #HU214</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Compra #XT266</t>
+          <t>Compra #HF603</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Compra #HS294</t>
+          <t>Compra #SN369</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Compra #AS540</t>
+          <t>Compra #SE300</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Compra #EA732</t>
+          <t>Compra #NU186</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>7</v>
       </c>
       <c r="D92" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E92" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Compra #FT017</t>
+          <t>Compra #NA136</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E93" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Compra #ET300</t>
+          <t>Compra #FX116</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E94" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Compra #NE368</t>
+          <t>Compra #UF491</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Compra #TT150</t>
+          <t>Compra #AN543</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Compra #AA149</t>
+          <t>Compra #UF778</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E97" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Compra #EN301</t>
+          <t>Compra #HH744</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E98" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Compra #HF839</t>
+          <t>Compra #AH176</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E99" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Compra #FH176</t>
+          <t>Compra #EF993</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E100" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Compra #ST247</t>
+          <t>Compra #SE368</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E101" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Compra #FU161</t>
+          <t>Compra #TU599</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2579,12 +2579,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Compra #UA653</t>
+          <t>Compra #HF912</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2600,862 +2600,862 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Compra #UE879</t>
+          <t>Compra #XE857</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
         <v>12</v>
       </c>
       <c r="E104" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Compra #SS570</t>
+          <t>Compra #HE659</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E105" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Compra #HN112</t>
+          <t>Compra #ET856</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E106" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Compra #EX594</t>
+          <t>Compra #NE955</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E107" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Compra #ST290</t>
+          <t>Compra #EN771</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E108" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Compra #EU350</t>
+          <t>Compra #FT577</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Compra #NA812</t>
+          <t>Compra #SE951</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Compra #UE244</t>
+          <t>Compra #AT723</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Compra #ST087</t>
+          <t>Compra #HT993</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
+        <v>12</v>
+      </c>
+      <c r="E112" t="n">
         <v>20</v>
-      </c>
-      <c r="E112" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Compra #UH038</t>
+          <t>Compra #FN068</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
+        <v>20</v>
+      </c>
+      <c r="E113" t="n">
         <v>27</v>
-      </c>
-      <c r="E113" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Compra #FT486</t>
+          <t>Compra #AU579</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>7</v>
       </c>
       <c r="D114" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E114" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Compra #NE779</t>
+          <t>Compra #AU403</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E115" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Compra #AF003</t>
+          <t>Compra #TT176</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E116" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Compra #HF595</t>
+          <t>Compra #FS666</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Compra #XU699</t>
+          <t>Compra #AF400</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E118" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Compra #HE785</t>
+          <t>Compra #XU387</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E119" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Compra #HE390</t>
+          <t>Compra #UN057</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D120" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E120" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Compra #HS206</t>
+          <t>Compra #TN321</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E121" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Compra #XS810</t>
+          <t>Compra #NE718</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E122" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Compra #NH267</t>
+          <t>Compra #NE255</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E123" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Compra #XS657</t>
+          <t>Compra #HU556</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>María Diana</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E124" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Compra #AA248</t>
+          <t>Compra #XE105</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Compra #HU685</t>
+          <t>Compra #UX040</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D126" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Compra #HN767</t>
+          <t>Compra #NS699</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E127" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Compra #TF596</t>
+          <t>Compra #EA392</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>5</v>
       </c>
       <c r="D128" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E128" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Compra #HF447</t>
+          <t>Compra #FN156</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E129" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Compra #XX825</t>
+          <t>Compra #NS042</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>7</v>
       </c>
       <c r="D130" t="n">
+        <v>34</v>
+      </c>
+      <c r="E130" t="n">
         <v>41</v>
-      </c>
-      <c r="E130" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Compra #AN010</t>
+          <t>Compra #EN103</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E131" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Compra #UA149</t>
+          <t>Compra #UA562</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D132" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Compra #EH893</t>
+          <t>Compra #FS478</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E133" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Compra #SA982</t>
+          <t>Compra #FU992</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E134" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Compra #HH255</t>
+          <t>Compra #HN230</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E135" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Compra #EH587</t>
+          <t>Compra #HN560</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E136" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Compra #UA928</t>
+          <t>Compra #FX655</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E137" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Compra #NH405</t>
+          <t>Compra #UU720</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>5</v>
       </c>
       <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
         <v>5</v>
-      </c>
-      <c r="E138" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Compra #NA773</t>
+          <t>Compra #EU268</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>6</v>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E139" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Compra #FX608</t>
+          <t>Compra #ES790</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E140" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Compra #TT682</t>
+          <t>Compra #ST306</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E141" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Compra #EU360</t>
+          <t>Compra #FE688</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D142" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E142" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Compra #AX893</t>
+          <t>Compra #EU985</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E143" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Compra #NH080</t>
+          <t>Compra #AH466</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E144" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
